--- a/MetaData/Paris-Nice.xlsx
+++ b/MetaData/Paris-Nice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="2011" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="228">
   <si>
     <t>NUM</t>
   </si>
@@ -1068,8 +1068,8 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
@@ -1156,7 +1156,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
